--- a/docs/table/报价测试数据/v2/报价系统模板0723.xlsx
+++ b/docs/table/报价测试数据/v2/报价系统模板0723.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\docs\table\报价测试数据\v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE9BC52-CEE4-4089-864D-050925565653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398A2A1F-6186-44AB-B561-CA78D9C13723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="客户料号与宏丰料号的关系" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="138">
   <si>
     <t>项次</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -603,6 +603,21 @@
   </si>
   <si>
     <t>W-1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00137</t>
+  </si>
+  <si>
+    <t>00002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AgC3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -745,7 +760,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -783,11 +798,18 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1086,13 +1108,13 @@
       <c r="A1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>117</v>
       </c>
       <c r="E1" s="7" t="s">
@@ -1154,13 +1176,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
@@ -2058,7 +2080,7 @@
   <cols>
     <col min="1" max="1" width="12.875" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="10" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="18" customWidth="1"/>
     <col min="4" max="4" width="19.625" style="10" customWidth="1"/>
     <col min="5" max="5" width="13.125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.125" style="10" customWidth="1"/>
@@ -2075,7 +2097,7 @@
       <c r="B1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="8" t="s">
@@ -2110,8 +2132,8 @@
       <c r="B2" s="9">
         <v>1</v>
       </c>
-      <c r="C2" s="9">
-        <v>991</v>
+      <c r="C2" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>112</v>
@@ -2131,7 +2153,7 @@
       <c r="B3" s="9">
         <v>2</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="17">
         <v>992</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -2152,7 +2174,7 @@
       <c r="B4" s="9">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="17" t="s">
         <v>129</v>
       </c>
       <c r="D4" s="9" t="s">
@@ -2175,11 +2197,11 @@
       <c r="B5" s="9">
         <v>4</v>
       </c>
-      <c r="C5" s="9">
-        <v>992</v>
+      <c r="C5" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -2188,12 +2210,12 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
     </row>
     <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
@@ -2202,7 +2224,7 @@
       <c r="B6" s="9">
         <v>5</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="17" t="s">
         <v>133</v>
       </c>
       <c r="D6" s="9" t="s">
@@ -2217,15 +2239,15 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
     </row>
     <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2234,15 +2256,15 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
     </row>
     <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="C8" s="17"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -2251,15 +2273,15 @@
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
     </row>
     <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -2268,15 +2290,15 @@
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
     </row>
     <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -2285,15 +2307,15 @@
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
@@ -2302,15 +2324,15 @@
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -2319,15 +2341,15 @@
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="C13" s="17"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
@@ -2336,15 +2358,15 @@
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
     </row>
     <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
@@ -2353,15 +2375,15 @@
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
@@ -2370,15 +2392,15 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
     </row>
     <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -2387,15 +2409,15 @@
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -2404,15 +2426,15 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -2421,15 +2443,15 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
     </row>
     <row r="19" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -2438,15 +2460,15 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
     </row>
     <row r="20" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -2455,15 +2477,15 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="C21" s="17"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -2472,15 +2494,15 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="C22" s="17"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -2489,15 +2511,15 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="C23" s="17"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -2506,15 +2528,15 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="C24" s="17"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -2527,7 +2549,7 @@
     <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="C25" s="17"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -2540,7 +2562,7 @@
     <row r="26" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="C26" s="17"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -2553,7 +2575,7 @@
     <row r="27" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="C27" s="17"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -2566,7 +2588,7 @@
     <row r="28" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="C28" s="17"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -2579,7 +2601,7 @@
     <row r="29" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="C29" s="17"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -2592,7 +2614,7 @@
     <row r="30" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="C30" s="17"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -2605,7 +2627,7 @@
     <row r="31" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="C31" s="17"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -2618,7 +2640,7 @@
     <row r="32" spans="1:17" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
+      <c r="C32" s="17"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
@@ -2631,7 +2653,7 @@
     <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+      <c r="C33" s="17"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -2660,7 +2682,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="10" customWidth="1"/>
+    <col min="2" max="2" width="16" style="18" customWidth="1"/>
     <col min="3" max="3" width="21.25" style="10" customWidth="1"/>
     <col min="4" max="4" width="5.375" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="10" bestFit="1" customWidth="1"/>
@@ -2677,7 +2699,7 @@
       <c r="A1" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="16" t="s">
         <v>119</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -2712,8 +2734,8 @@
       <c r="A2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="9">
-        <v>991</v>
+      <c r="B2" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>112</v>
@@ -2741,7 +2763,7 @@
       <c r="A3" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="17">
         <v>992</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -2768,17 +2790,17 @@
       <c r="A4" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="9">
-        <v>991</v>
+      <c r="B4" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D4" s="9">
         <v>1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
@@ -2788,11 +2810,21 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
+      <c r="A5" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>137</v>
+      </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -2802,7 +2834,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2815,7 +2847,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2828,7 +2860,7 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2841,7 +2873,7 @@
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2854,7 +2886,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2867,7 +2899,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2880,7 +2912,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2893,7 +2925,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -2906,7 +2938,7 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -2919,7 +2951,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -2932,7 +2964,7 @@
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -2945,7 +2977,7 @@
     </row>
     <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -2958,7 +2990,7 @@
     </row>
     <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
@@ -2971,7 +3003,7 @@
     </row>
     <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -2984,7 +3016,7 @@
     </row>
     <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
@@ -2997,7 +3029,7 @@
     </row>
     <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -3010,7 +3042,7 @@
     </row>
     <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -3023,7 +3055,7 @@
     </row>
     <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -3036,7 +3068,7 @@
     </row>
     <row r="24" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
+      <c r="B24" s="17"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -3049,7 +3081,7 @@
     </row>
     <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -3062,7 +3094,7 @@
     </row>
     <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -3075,7 +3107,7 @@
     </row>
     <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
@@ -3088,7 +3120,7 @@
     </row>
     <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -3101,7 +3133,7 @@
     </row>
     <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
@@ -3114,7 +3146,7 @@
     </row>
     <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -3127,7 +3159,7 @@
     </row>
     <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
@@ -3251,7 +3283,7 @@
   <cols>
     <col min="1" max="1" width="15.25" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" style="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.25" style="10" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="10" bestFit="1" customWidth="1"/>
@@ -3272,7 +3304,7 @@
       <c r="B1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="8" t="s">
@@ -3313,8 +3345,8 @@
       <c r="B2" s="9">
         <v>1</v>
       </c>
-      <c r="C2" s="9">
-        <v>991</v>
+      <c r="C2" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>112</v>
@@ -3342,7 +3374,7 @@
       <c r="B3" s="9">
         <v>3</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="17">
         <v>992</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -3367,7 +3399,7 @@
     <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="C4" s="17"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
@@ -3382,7 +3414,7 @@
     <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -3397,7 +3429,7 @@
     <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
@@ -3410,7 +3442,7 @@
       <c r="M6" s="9"/>
     </row>
     <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C7" s="9"/>
+      <c r="C7" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
